--- a/survey_templates/035_water_quality_inspection_form--survey_templates.xlsx
+++ b/survey_templates/035_water_quality_inspection_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'lake',_'value':_'lake'}</t>
+          <t>lake</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'lake', 'value': 'lake'}</t>
+          <t>lake</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'river',_'value':_'river'}</t>
+          <t>river</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'river', 'value': 'river'}</t>
+          <t>river</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'pond',_'value':_'pond'}</t>
+          <t>pond</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'pond', 'value': 'pond'}</t>
+          <t>pond</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_20,_'name':_'blue',_'value':_'blue'}</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 20, 'name': 'blue', 'value': 'blue'}</t>
+          <t>blue</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_21,_'name':_'green',_'value':_'green'}</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 21, 'name': 'green', 'value': 'green'}</t>
+          <t>green</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_22,_'name':_'brown',_'value':_'brown'}</t>
+          <t>brown</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 22, 'name': 'brown', 'value': 'brown'}</t>
+          <t>brown</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_30,_'name':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 30, 'name': 'none', 'value': 'none'}</t>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_31,_'name':_'mild',_'value':_'mild'}</t>
+          <t>mild</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 31, 'name': 'mild', 'value': 'mild'}</t>
+          <t>mild</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_32,_'name':_'moderate',_'value':_'moderate'}</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 32, 'name': 'moderate', 'value': 'moderate'}</t>
+          <t>moderate</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_33,_'name':_'strong',_'value':_'strong'}</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 33, 'name': 'strong', 'value': 'strong'}</t>
+          <t>strong</t>
         </is>
       </c>
     </row>
